--- a/data/2024/11-caras-severin/50790-resita/budget_file.xlsx
+++ b/data/2024/11-caras-severin/50790-resita/budget_file.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>07.02 total_2024: parent 22.095,79 != sum(children) 39.941,58 (4 children); 07.02 trim4: parent 1.660,00 != sum(children) 2.890,00 (4 children); 07.02 trim3: parent 4.270,62 != sum(children) 8.061,24 (4 children); 07.02 est2026: parent 117.500,00 != sum(children) 211.500,00 (4 children); 07.02 est2024: parent 74.000,00 != sum(children) 133.000,00 (4 children); 07.02 trim1: parent 7.495,17 != sum(children) 13.600,34 (4 children); 07.02 trim2: parent 8.670,00 != sum(children) 15.390,00 (4 children); 07.02 est2027: parent 31.200,00 != sum(children) 57.300,00 (4 children)</t>
+          <t>07.02 trim4: parent 1.660,00 != sum(children) 2.890,00 (4 children); 07.02 est2027: parent 31.200,00 != sum(children) 57.300,00 (4 children); 07.02 trim2: parent 8.670,00 != sum(children) 15.390,00 (4 children); 07.02 trim1: parent 7.495,17 != sum(children) 13.600,34 (4 children); 07.02 est2026: parent 117.500,00 != sum(children) 211.500,00 (4 children); 07.02 total_2024: parent 22.095,79 != sum(children) 39.941,58 (4 children); 07.02 trim3: parent 4.270,62 != sum(children) 8.061,24 (4 children); 07.02 est2024: parent 74.000,00 != sum(children) 133.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>11.02 total_2024: parent 56.751,15 != sum(children) 17.215,00 (3 children); 11.02 trim4: parent 7.113,00 != sum(children) 849,00 (3 children); 11.02 trim3: parent 11.689,00 != sum(children) 733,00 (3 children); 11.02 est2026: parent 44.514,15 != sum(children) 3.909,00 (3 children); 11.02 est2024: parent 43.931,15 != sum(children) 3.916,00 (3 children); 11.02 trim1: parent 24.527,15 != sum(children) 14.073,00 (3 children); 11.02 trim2: parent 13.422,00 != sum(children) 1.560,00 (3 children); 11.02 est2027: parent 44.659,15 != sum(children) 3.909,00 (3 children)</t>
+          <t>11.02 trim4: parent 7.113,00 != sum(children) 849,00 (3 children); 11.02 est2027: parent 44.659,15 != sum(children) 3.909,00 (3 children); 11.02 trim2: parent 13.422,00 != sum(children) 1.560,00 (3 children); 11.02 trim1: parent 24.527,15 != sum(children) 14.073,00 (3 children); 11.02 total_2024: parent 56.751,15 != sum(children) 17.215,00 (3 children); 11.02 est2026: parent 44.514,15 != sum(children) 3.909,00 (3 children); 11.02 trim3: parent 11.689,00 != sum(children) 733,00 (3 children); 11.02 est2024: parent 43.931,15 != sum(children) 3.916,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>42.02 total_2024: parent 212.757,37 != sum(children) 190.952,36 (10 children); 42.02 trim4: parent 69.584,01 != sum(children) 59.446,24 (10 children); 42.02 trim3: parent 21.120,27 != sum(children) 9.493,76 (10 children); 42.02 est2026: parent 88.355,12 != sum(children) 82.596,04 (10 children); 42.02 est2024: parent 160.654,41 != sum(children) 156.179,69 (10 children); 42.02 trim1: parent 62.112,16 != sum(children) 62.096,16 (10 children); 42.02 trim2: parent 59.940,93 != sum(children) 59.916,20 (10 children)</t>
+          <t>42.02 trim4: parent 69.584,01 != sum(children) 59.446,24 (10 children); 42.02 trim2: parent 59.940,93 != sum(children) 59.916,20 (10 children); 42.02 trim1: parent 62.112,16 != sum(children) 62.096,16 (10 children); 42.02 est2026: parent 88.355,12 != sum(children) 82.596,04 (10 children); 42.02 total_2024: parent 212.757,37 != sum(children) 190.952,36 (10 children); 42.02 trim3: parent 21.120,27 != sum(children) 9.493,76 (10 children); 42.02 est2024: parent 160.654,41 != sum(children) 156.179,69 (10 children)</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
-          <t>45.02.48 total_2024: parent 0,00 != sum(children) 126.891,19 (2 children); 45.02.48 trim4: parent 0,00 != sum(children) 58.676,19 (2 children); 45.02.48 trim3: parent 0,00 != sum(children) 68.080,00 (2 children); 45.02.48 est2026: parent 0,00 != sum(children) 28.915,40 (2 children); 45.02.48 est2024: parent 0,00 != sum(children) 29.148,90 (2 children); 45.02.48 trim2: parent 0,00 != sum(children) 135,00 (2 children)</t>
+          <t>45.02.48 trim4: parent 0,00 != sum(children) 58.676,19 (2 children); 45.02.48 trim2: parent 0,00 != sum(children) 135,00 (2 children); 45.02.48 total_2024: parent 0,00 != sum(children) 126.891,19 (2 children); 45.02.48 est2026: parent 0,00 != sum(children) 28.915,40 (2 children); 45.02.48 trim3: parent 0,00 != sum(children) 68.080,00 (2 children); 45.02.48 est2024: parent 0,00 != sum(children) 29.148,90 (2 children)</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>50.02 total_2024: parent 2.957,76 != sum(children) 135.412,33 (2 children); 50.02 trim4: parent 163.699,24 != sum(children) 31.126,08 (2 children); 50.02 trim3: parent 201.030,15 != sum(children) 29.683,56 (2 children); 50.02 est2026: parent 534.465,80 != sum(children) 289.551,61 (2 children); 50.02 est2024: parent 654.943,92 != sum(children) 197.921,55 (2 children); 50.02 trim1: parent 152.036,92 != sum(children) 49.833,70 (2 children); 50.02 trim2: parent 116.879,00 != sum(children) 24.768,99 (2 children); 50.02 est2027: parent 203.521,15 != sum(children) 68.500,00 (2 children)</t>
+          <t>50.02 trim4: parent 163.699,24 != sum(children) 31.126,08 (2 children); 50.02 est2027: parent 203.521,15 != sum(children) 68.500,00 (2 children); 50.02 trim2: parent 116.879,00 != sum(children) 24.768,99 (2 children); 50.02 trim1: parent 152.036,92 != sum(children) 49.833,70 (2 children); 50.02 est2026: parent 534.465,80 != sum(children) 289.551,61 (2 children); 50.02 total_2024: parent 2.957,76 != sum(children) 135.412,33 (2 children); 50.02 trim3: parent 201.030,15 != sum(children) 29.683,56 (2 children); 50.02 est2024: parent 654.943,92 != sum(children) 197.921,55 (2 children)</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="Q112" s="5" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 327,80 != sum(children) 31.150,80 (9 children); 20.01 total: parent 38.528,98 != sum(children) 6.374,98 (9 children); 20.01 trim4: parent 2.305,63 != sum(children) 2.271,63 (9 children); 20.01 trim3: parent 13.462,51 != sum(children) 13.095,51 (9 children); 20.01 trim1: parent 13.216,29 != sum(children) 12.533,29 (9 children); 20.01 trim2: parent 9.544,55 != sum(children) 9.297,55 (9 children)</t>
+          <t>20.01 trim4: parent 2.305,63 != sum(children) 2.271,63 (9 children); 20.01 trim2: parent 9.544,55 != sum(children) 9.297,55 (9 children); 20.01 trim1: parent 13.216,29 != sum(children) 12.533,29 (9 children); 20.01 total_2024: parent 327,80 != sum(children) 31.150,80 (9 children); 20.01 trim3: parent 13.462,51 != sum(children) 13.095,51 (9 children); 20.01 total: parent 38.528,98 != sum(children) 6.374,98 (9 children)</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>57.02 total_2024: parent 30.272,00 != sum(children) 24.527,00 (2 children); 57.02 trim4: parent 4.571,00 != sum(children) 3.794,00 (2 children); 57.02 trim3: parent 8.345,50 != sum(children) 7.133,00 (2 children); 57.02 trim1: parent 8.418,00 != sum(children) 6.589,00 (2 children); 57.02 trim2: parent 8.937,50 != sum(children) 7.011,00 (2 children)</t>
+          <t>57.02 trim4: parent 4.571,00 != sum(children) 3.794,00 (2 children); 57.02 trim2: parent 8.937,50 != sum(children) 7.011,00 (2 children); 57.02 trim1: parent 8.418,00 != sum(children) 6.589,00 (2 children); 57.02 total_2024: parent 30.272,00 != sum(children) 24.527,00 (2 children); 57.02 trim3: parent 8.345,50 != sum(children) 7.133,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="Q218" s="5" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 10.534,70 != sum(children) 10.219,70 (4 children); 20 trim4: parent 1.173,60 != sum(children) 1.123,60 (4 children); 20 trim3: parent 3.333,70 != sum(children) 3.283,70 (4 children); 20 trim1: parent 3.534,00 != sum(children) 3.369,00 (4 children); 20 trim2: parent 2.493,40 != sum(children) 2.443,40 (4 children)</t>
+          <t>20 trim4: parent 1.173,60 != sum(children) 1.123,60 (4 children); 20 trim2: parent 2.493,40 != sum(children) 2.443,40 (4 children); 20 trim1: parent 3.534,00 != sum(children) 3.369,00 (4 children); 20 total_2024: parent 10.534,70 != sum(children) 10.219,70 (4 children); 20 trim3: parent 3.333,70 != sum(children) 3.283,70 (4 children)</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="Q292" s="5" t="inlineStr">
         <is>
-          <t>65.02 trim2: parent 5.237,79 != sum(children) 52,00 (1 children); 65.02 total_2024: parent 17.550,70 != sum(children) 60,15 (1 children); 65.02 trim1: parent 5.058,97 != sum(children) 8,15 (1 children)</t>
+          <t>65.02 trim2: parent 5.237,79 != sum(children) 52,00 (1 children); 65.02 trim1: parent 5.058,97 != sum(children) 8,15 (1 children); 65.02 total_2024: parent 17.550,70 != sum(children) 60,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="Q295" s="5" t="inlineStr">
         <is>
-          <t>10.01 total_2024: parent 415,00 != sum(children) 203,00 (2 children); 10.01 trim4: parent 76,50 != sum(children) 30,50 (2 children); 10.01 trim3: parent 77,50 != sum(children) 31,50 (2 children); 10.01 trim1: parent 131,00 != sum(children) 71,00 (2 children); 10.01 trim2: parent 130,00 != sum(children) 70,00 (2 children)</t>
+          <t>10.01 trim4: parent 76,50 != sum(children) 30,50 (2 children); 10.01 trim2: parent 130,00 != sum(children) 70,00 (2 children); 10.01 trim1: parent 131,00 != sum(children) 71,00 (2 children); 10.01 total_2024: parent 415,00 != sum(children) 203,00 (2 children); 10.01 trim3: parent 77,50 != sum(children) 31,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="Q331" s="5" t="inlineStr">
         <is>
-          <t>57.02 total_2024: parent 7.502,00 != sum(children) 4.257,00 (2 children); 57.02 trim4: parent 1.706,00 != sum(children) 1.329,00 (2 children); 57.02 trim3: parent 1.540,50 != sum(children) 1.028,00 (2 children); 57.02 trim1: parent 2.093,00 != sum(children) 964,00 (2 children); 57.02 trim2: parent 2.162,50 != sum(children) 936,00 (2 children)</t>
+          <t>57.02 trim4: parent 1.706,00 != sum(children) 1.329,00 (2 children); 57.02 trim2: parent 2.162,50 != sum(children) 936,00 (2 children); 57.02 trim1: parent 2.093,00 != sum(children) 964,00 (2 children); 57.02 total_2024: parent 7.502,00 != sum(children) 4.257,00 (2 children); 57.02 trim3: parent 1.540,50 != sum(children) 1.028,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="Q365" s="5" t="inlineStr">
         <is>
-          <t>20.04 total_2024: parent 135,00 != sum(children) 99,00 (2 children); 20.04 trim4: parent 14,00 != sum(children) 11,00 (2 children); 20.04 trim3: parent 24,00 != sum(children) 16,00 (2 children); 20.04 trim1: parent 48,00 != sum(children) 33,00 (2 children); 20.04 trim2: parent 49,00 != sum(children) 39,00 (2 children)</t>
+          <t>20.04 trim4: parent 14,00 != sum(children) 11,00 (2 children); 20.04 trim2: parent 49,00 != sum(children) 39,00 (2 children); 20.04 trim1: parent 48,00 != sum(children) 33,00 (2 children); 20.04 total_2024: parent 135,00 != sum(children) 99,00 (2 children); 20.04 trim3: parent 24,00 != sum(children) 16,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -18475,7 +18475,7 @@
       </c>
       <c r="Q373" s="5" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 5.871,30 != sum(children) 3,55 (1 children); 67.02 total_2024: parent 22.404,85 != sum(children) 149,05 (1 children); 67.02 trim1: parent 7.985,50 != sum(children) 74,50 (1 children); 67.02 trim3: parent 5.149,55 != sum(children) 71,00 (1 children)</t>
+          <t>67.02 trim2: parent 5.871,30 != sum(children) 3,55 (1 children); 67.02 trim1: parent 7.985,50 != sum(children) 74,50 (1 children); 67.02 total_2024: parent 22.404,85 != sum(children) 149,05 (1 children); 67.02 trim3: parent 5.149,55 != sum(children) 71,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="Q422" s="5" t="inlineStr">
         <is>
-          <t>68.02 trim2: parent 11.230,30 != sum(children) 108,00 (1 children); 68.02 total_2024: parent 36.786,00 != sum(children) 138,00 (1 children); 68.02 trim1: parent 11.285,20 != sum(children) 30,00 (1 children)</t>
+          <t>68.02 trim2: parent 11.230,30 != sum(children) 108,00 (1 children); 68.02 trim1: parent 11.285,20 != sum(children) 30,00 (1 children); 68.02 total_2024: parent 36.786,00 != sum(children) 138,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="Q434" s="5" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 1.825,00 != sum(children) 1.785,00 (8 children); 20.01 trim4: parent 102,35 != sum(children) 92,35 (8 children); 20.01 trim3: parent 108,05 != sum(children) 98,05 (8 children); 20.01 trim1: parent 1.129,30 != sum(children) 1.119,30 (8 children); 20.01 trim2: parent 485,30 != sum(children) 475,30 (8 children)</t>
+          <t>20.01 trim4: parent 102,35 != sum(children) 92,35 (8 children); 20.01 trim2: parent 485,30 != sum(children) 475,30 (8 children); 20.01 trim1: parent 1.129,30 != sum(children) 1.119,30 (8 children); 20.01 total_2024: parent 1.825,00 != sum(children) 1.785,00 (8 children); 20.01 trim3: parent 108,05 != sum(children) 98,05 (8 children)</t>
         </is>
       </c>
     </row>
@@ -23115,7 +23115,7 @@
       </c>
       <c r="Q468" s="5" t="inlineStr">
         <is>
-          <t>71.01 total_2024: parent 138,00 != sum(children) 50,70 (3 children); 71.01 trim2: parent 108,00 != sum(children) 18,00 (3 children); 71.01 trim3: parent 0,00 != sum(children) 2,70 (3 children)</t>
+          <t>71.01 trim2: parent 108,00 != sum(children) 18,00 (3 children); 71.01 total_2024: parent 138,00 != sum(children) 50,70 (3 children); 71.01 trim3: parent 0,00 != sum(children) 2,70 (3 children)</t>
         </is>
       </c>
     </row>
@@ -23657,7 +23657,7 @@
       </c>
       <c r="Q479" s="5" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 485.803,89 != sum(children) 135.037,13 (2 children); 70.02 trim4: parent 143.895,26 != sum(children) 31.123,08 (2 children); 70.02 trim3: parent 164.605,24 != sum(children) 29.587,56 (2 children); 70.02 est2026: parent 417.259,65 != sum(children) 289.551,61 (2 children); 70.02 est2024: parent 537.737,77 != sum(children) 197.921,55 (2 children); 70.02 trim1: parent 100.149,05 != sum(children) 49.721,05 (2 children); 70.02 trim2: parent 77.154,34 != sum(children) 24.605,44 (2 children); 70.02 est2027: parent 82.240,00 != sum(children) 68.500,00 (2 children)</t>
+          <t>70.02 trim4: parent 143.895,26 != sum(children) 31.123,08 (2 children); 70.02 est2027: parent 82.240,00 != sum(children) 68.500,00 (2 children); 70.02 trim2: parent 77.154,34 != sum(children) 24.605,44 (2 children); 70.02 trim1: parent 100.149,05 != sum(children) 49.721,05 (2 children); 70.02 est2026: parent 417.259,65 != sum(children) 289.551,61 (2 children); 70.02 total_2024: parent 485.803,89 != sum(children) 135.037,13 (2 children); 70.02 trim3: parent 164.605,24 != sum(children) 29.587,56 (2 children); 70.02 est2024: parent 537.737,77 != sum(children) 197.921,55 (2 children)</t>
         </is>
       </c>
     </row>
@@ -24257,7 +24257,7 @@
       </c>
       <c r="Q491" s="5" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 14.731,99 != sum(children) 4.975,60 (7 children); 20.01 trim4: parent 259,60 != sum(children) 559,60 (7 children); 20.01 trim3: parent 7.190,99 != sum(children) 1.180,00 (7 children); 20.01 trim1: parent 4.316,40 != sum(children) 1.471,00 (7 children); 20.01 trim2: parent 2.965,00 != sum(children) 1.765,00 (7 children)</t>
+          <t>20.01 trim4: parent 259,60 != sum(children) 559,60 (7 children); 20.01 trim2: parent 2.965,00 != sum(children) 1.765,00 (7 children); 20.01 trim1: parent 4.316,40 != sum(children) 1.471,00 (7 children); 20.01 total_2024: parent 14.731,99 != sum(children) 4.975,60 (7 children); 20.01 trim3: parent 7.190,99 != sum(children) 1.180,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="Q526" s="5" t="inlineStr">
         <is>
-          <t>58 total_2024: parent 21.548,02 != sum(children) 2.521,00 (2 children); 58 trim4: parent 2.951,01 != sum(children) 10,00 (2 children); 58 trim3: parent 3.246,81 != sum(children) 2.220,00 (2 children); 58 trim1: parent 8.024,00 != sum(children) 71,00 (2 children); 58 trim2: parent 7.326,20 != sum(children) 220,00 (2 children)</t>
+          <t>58 trim4: parent 2.951,01 != sum(children) 10,00 (2 children); 58 trim2: parent 7.326,20 != sum(children) 220,00 (2 children); 58 trim1: parent 8.024,00 != sum(children) 71,00 (2 children); 58 total_2024: parent 21.548,02 != sum(children) 2.521,00 (2 children); 58 trim3: parent 3.246,81 != sum(children) 2.220,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -28605,7 +28605,7 @@
       </c>
       <c r="Q581" s="5" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 2.325,30 != sum(children) 2.209,80 (9 children); 20.01 trim4: parent -385,20 != sum(children) -391,70 (9 children); 20.01 trim3: parent 892,10 != sum(children) 883,10 (9 children); 20.01 trim1: parent 1.402,50 != sum(children) 1.372,50 (9 children); 20.01 trim2: parent 415,90 != sum(children) 345,90 (9 children)</t>
+          <t>20.01 trim4: parent -385,20 != sum(children) -391,70 (9 children); 20.01 trim2: parent 415,90 != sum(children) 345,90 (9 children); 20.01 trim1: parent 1.402,50 != sum(children) 1.372,50 (9 children); 20.01 total_2024: parent 2.325,30 != sum(children) 2.209,80 (9 children); 20.01 trim3: parent 892,10 != sum(children) 883,10 (9 children)</t>
         </is>
       </c>
     </row>
@@ -59844,12 +59844,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>07.02 total_2024: parent 22.095,79 != sum(children) 39.941,58 (4 children)</t>
+          <t>07.02 trim4: parent 1.660,00 != sum(children) 2.890,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -59874,12 +59874,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07.02 trim4: parent 1.660,00 != sum(children) 2.890,00 (4 children)</t>
+          <t>07.02 est2027: parent 31.200,00 != sum(children) 57.300,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -59904,12 +59904,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>07.02 trim3: parent 4.270,62 != sum(children) 8.061,24 (4 children)</t>
+          <t>07.02 trim2: parent 8.670,00 != sum(children) 15.390,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -59934,12 +59934,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>07.02 est2026: parent 117.500,00 != sum(children) 211.500,00 (4 children)</t>
+          <t>07.02 trim1: parent 7.495,17 != sum(children) 13.600,34 (4 children)</t>
         </is>
       </c>
     </row>
@@ -59964,12 +59964,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07.02 est2024: parent 74.000,00 != sum(children) 133.000,00 (4 children)</t>
+          <t>07.02 est2026: parent 117.500,00 != sum(children) 211.500,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -59994,12 +59994,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07.02 trim1: parent 7.495,17 != sum(children) 13.600,34 (4 children)</t>
+          <t>07.02 total_2024: parent 22.095,79 != sum(children) 39.941,58 (4 children)</t>
         </is>
       </c>
     </row>
@@ -60024,12 +60024,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07.02 trim2: parent 8.670,00 != sum(children) 15.390,00 (4 children)</t>
+          <t>07.02 trim3: parent 4.270,62 != sum(children) 8.061,24 (4 children)</t>
         </is>
       </c>
     </row>
@@ -60054,12 +60054,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 31.200,00 != sum(children) 57.300,00 (4 children)</t>
+          <t>07.02 est2024: parent 74.000,00 != sum(children) 133.000,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -60109,12 +60109,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11.02 total_2024: parent 56.751,15 != sum(children) 17.215,00 (3 children)</t>
+          <t>11.02 trim4: parent 7.113,00 != sum(children) 849,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60139,12 +60139,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11.02 trim4: parent 7.113,00 != sum(children) 849,00 (3 children)</t>
+          <t>11.02 est2027: parent 44.659,15 != sum(children) 3.909,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60169,12 +60169,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11.02 trim3: parent 11.689,00 != sum(children) 733,00 (3 children)</t>
+          <t>11.02 trim2: parent 13.422,00 != sum(children) 1.560,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60199,12 +60199,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11.02 est2026: parent 44.514,15 != sum(children) 3.909,00 (3 children)</t>
+          <t>11.02 trim1: parent 24.527,15 != sum(children) 14.073,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60229,12 +60229,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11.02 est2024: parent 43.931,15 != sum(children) 3.916,00 (3 children)</t>
+          <t>11.02 total_2024: parent 56.751,15 != sum(children) 17.215,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60259,12 +60259,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.02 trim1: parent 24.527,15 != sum(children) 14.073,00 (3 children)</t>
+          <t>11.02 est2026: parent 44.514,15 != sum(children) 3.909,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60289,12 +60289,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11.02 trim2: parent 13.422,00 != sum(children) 1.560,00 (3 children)</t>
+          <t>11.02 trim3: parent 11.689,00 != sum(children) 733,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60319,12 +60319,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11.02 est2027: parent 44.659,15 != sum(children) 3.909,00 (3 children)</t>
+          <t>11.02 est2024: parent 43.931,15 != sum(children) 3.916,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -60349,12 +60349,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.02 total_2024: parent 212.757,37 != sum(children) 190.952,36 (10 children)</t>
+          <t>42.02 trim4: parent 69.584,01 != sum(children) 59.446,24 (10 children)</t>
         </is>
       </c>
     </row>
@@ -60379,12 +60379,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42.02 trim4: parent 69.584,01 != sum(children) 59.446,24 (10 children)</t>
+          <t>42.02 trim2: parent 59.940,93 != sum(children) 59.916,20 (10 children)</t>
         </is>
       </c>
     </row>
@@ -60409,12 +60409,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.02 trim3: parent 21.120,27 != sum(children) 9.493,76 (10 children)</t>
+          <t>42.02 trim1: parent 62.112,16 != sum(children) 62.096,16 (10 children)</t>
         </is>
       </c>
     </row>
@@ -60469,12 +60469,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.02 est2024: parent 160.654,41 != sum(children) 156.179,69 (10 children)</t>
+          <t>42.02 total_2024: parent 212.757,37 != sum(children) 190.952,36 (10 children)</t>
         </is>
       </c>
     </row>
@@ -60499,12 +60499,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>42.02 trim1: parent 62.112,16 != sum(children) 62.096,16 (10 children)</t>
+          <t>42.02 trim3: parent 21.120,27 != sum(children) 9.493,76 (10 children)</t>
         </is>
       </c>
     </row>
@@ -60529,12 +60529,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>42.02 trim2: parent 59.940,93 != sum(children) 59.916,20 (10 children)</t>
+          <t>42.02 est2024: parent 160.654,41 != sum(children) 156.179,69 (10 children)</t>
         </is>
       </c>
     </row>
@@ -60589,12 +60589,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>45.02.48 total_2024: parent 0,00 != sum(children) 126.891,19 (2 children)</t>
+          <t>45.02.48 trim4: parent 0,00 != sum(children) 58.676,19 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60619,12 +60619,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>45.02.48 trim4: parent 0,00 != sum(children) 58.676,19 (2 children)</t>
+          <t>45.02.48 trim2: parent 0,00 != sum(children) 135,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60649,12 +60649,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>45.02.48 trim3: parent 0,00 != sum(children) 68.080,00 (2 children)</t>
+          <t>45.02.48 total_2024: parent 0,00 != sum(children) 126.891,19 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60709,12 +60709,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>45.02.48 est2024: parent 0,00 != sum(children) 29.148,90 (2 children)</t>
+          <t>45.02.48 trim3: parent 0,00 != sum(children) 68.080,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60739,12 +60739,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>45.02.48 trim2: parent 0,00 != sum(children) 135,00 (2 children)</t>
+          <t>45.02.48 est2024: parent 0,00 != sum(children) 29.148,90 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60769,12 +60769,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>50.02 total_2024: parent 2.957,76 != sum(children) 135.412,33 (2 children)</t>
+          <t>50.02 trim4: parent 163.699,24 != sum(children) 31.126,08 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60799,12 +60799,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>50.02 trim4: parent 163.699,24 != sum(children) 31.126,08 (2 children)</t>
+          <t>50.02 est2027: parent 203.521,15 != sum(children) 68.500,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60829,12 +60829,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>50.02 trim3: parent 201.030,15 != sum(children) 29.683,56 (2 children)</t>
+          <t>50.02 trim2: parent 116.879,00 != sum(children) 24.768,99 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60859,12 +60859,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>50.02 est2026: parent 534.465,80 != sum(children) 289.551,61 (2 children)</t>
+          <t>50.02 trim1: parent 152.036,92 != sum(children) 49.833,70 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60889,12 +60889,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>50.02 est2024: parent 654.943,92 != sum(children) 197.921,55 (2 children)</t>
+          <t>50.02 est2026: parent 534.465,80 != sum(children) 289.551,61 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60919,12 +60919,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>50.02 trim1: parent 152.036,92 != sum(children) 49.833,70 (2 children)</t>
+          <t>50.02 total_2024: parent 2.957,76 != sum(children) 135.412,33 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60949,12 +60949,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>50.02 trim2: parent 116.879,00 != sum(children) 24.768,99 (2 children)</t>
+          <t>50.02 trim3: parent 201.030,15 != sum(children) 29.683,56 (2 children)</t>
         </is>
       </c>
     </row>
@@ -60979,12 +60979,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>50.02 est2027: parent 203.521,15 != sum(children) 68.500,00 (2 children)</t>
+          <t>50.02 est2024: parent 654.943,92 != sum(children) 197.921,55 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61069,12 +61069,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 327,80 != sum(children) 31.150,80 (9 children)</t>
+          <t>20.01 trim4: parent 2.305,63 != sum(children) 2.271,63 (9 children)</t>
         </is>
       </c>
     </row>
@@ -61099,12 +61099,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20.01 total: parent 38.528,98 != sum(children) 6.374,98 (9 children)</t>
+          <t>20.01 trim2: parent 9.544,55 != sum(children) 9.297,55 (9 children)</t>
         </is>
       </c>
     </row>
@@ -61129,12 +61129,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 2.305,63 != sum(children) 2.271,63 (9 children)</t>
+          <t>20.01 trim1: parent 13.216,29 != sum(children) 12.533,29 (9 children)</t>
         </is>
       </c>
     </row>
@@ -61159,12 +61159,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 13.462,51 != sum(children) 13.095,51 (9 children)</t>
+          <t>20.01 total_2024: parent 327,80 != sum(children) 31.150,80 (9 children)</t>
         </is>
       </c>
     </row>
@@ -61189,12 +61189,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 13.216,29 != sum(children) 12.533,29 (9 children)</t>
+          <t>20.01 trim3: parent 13.462,51 != sum(children) 13.095,51 (9 children)</t>
         </is>
       </c>
     </row>
@@ -61219,12 +61219,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20.01 trim2: parent 9.544,55 != sum(children) 9.297,55 (9 children)</t>
+          <t>20.01 total: parent 38.528,98 != sum(children) 6.374,98 (9 children)</t>
         </is>
       </c>
     </row>
@@ -61249,12 +61249,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>57.02 total_2024: parent 30.272,00 != sum(children) 24.527,00 (2 children)</t>
+          <t>57.02 trim4: parent 4.571,00 != sum(children) 3.794,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61279,12 +61279,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>57.02 trim4: parent 4.571,00 != sum(children) 3.794,00 (2 children)</t>
+          <t>57.02 trim2: parent 8.937,50 != sum(children) 7.011,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61309,12 +61309,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>57.02 trim3: parent 8.345,50 != sum(children) 7.133,00 (2 children)</t>
+          <t>57.02 trim1: parent 8.418,00 != sum(children) 6.589,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61339,12 +61339,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>57.02 trim1: parent 8.418,00 != sum(children) 6.589,00 (2 children)</t>
+          <t>57.02 total_2024: parent 30.272,00 != sum(children) 24.527,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61369,12 +61369,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>57.02 trim2: parent 8.937,50 != sum(children) 7.011,00 (2 children)</t>
+          <t>57.02 trim3: parent 8.345,50 != sum(children) 7.133,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61424,12 +61424,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 10.534,70 != sum(children) 10.219,70 (4 children)</t>
+          <t>20 trim4: parent 1.173,60 != sum(children) 1.123,60 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61454,12 +61454,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20 trim4: parent 1.173,60 != sum(children) 1.123,60 (4 children)</t>
+          <t>20 trim2: parent 2.493,40 != sum(children) 2.443,40 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61484,12 +61484,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20 trim3: parent 3.333,70 != sum(children) 3.283,70 (4 children)</t>
+          <t>20 trim1: parent 3.534,00 != sum(children) 3.369,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61514,12 +61514,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20 trim1: parent 3.534,00 != sum(children) 3.369,00 (4 children)</t>
+          <t>20 total_2024: parent 10.534,70 != sum(children) 10.219,70 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61544,12 +61544,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20 trim2: parent 2.493,40 != sum(children) 2.443,40 (4 children)</t>
+          <t>20 trim3: parent 3.333,70 != sum(children) 3.283,70 (4 children)</t>
         </is>
       </c>
     </row>
@@ -61769,12 +61769,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.02 total_2024: parent 17.550,70 != sum(children) 60,15 (1 children)</t>
+          <t>65.02 trim1: parent 5.058,97 != sum(children) 8,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -61799,12 +61799,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>65.02 trim1: parent 5.058,97 != sum(children) 8,15 (1 children)</t>
+          <t>65.02 total_2024: parent 17.550,70 != sum(children) 60,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -61854,12 +61854,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10.01 total_2024: parent 415,00 != sum(children) 203,00 (2 children)</t>
+          <t>10.01 trim4: parent 76,50 != sum(children) 30,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61884,12 +61884,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10.01 trim4: parent 76,50 != sum(children) 30,50 (2 children)</t>
+          <t>10.01 trim2: parent 130,00 != sum(children) 70,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61914,12 +61914,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10.01 trim3: parent 77,50 != sum(children) 31,50 (2 children)</t>
+          <t>10.01 trim1: parent 131,00 != sum(children) 71,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61944,12 +61944,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10.01 trim1: parent 131,00 != sum(children) 71,00 (2 children)</t>
+          <t>10.01 total_2024: parent 415,00 != sum(children) 203,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -61974,12 +61974,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10.01 trim2: parent 130,00 != sum(children) 70,00 (2 children)</t>
+          <t>10.01 trim3: parent 77,50 != sum(children) 31,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62004,12 +62004,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>57.02 total_2024: parent 7.502,00 != sum(children) 4.257,00 (2 children)</t>
+          <t>57.02 trim4: parent 1.706,00 != sum(children) 1.329,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62034,12 +62034,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>57.02 trim4: parent 1.706,00 != sum(children) 1.329,00 (2 children)</t>
+          <t>57.02 trim2: parent 2.162,50 != sum(children) 936,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62064,12 +62064,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>57.02 trim3: parent 1.540,50 != sum(children) 1.028,00 (2 children)</t>
+          <t>57.02 trim1: parent 2.093,00 != sum(children) 964,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62094,12 +62094,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>57.02 trim1: parent 2.093,00 != sum(children) 964,00 (2 children)</t>
+          <t>57.02 total_2024: parent 7.502,00 != sum(children) 4.257,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62124,12 +62124,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>57.02 trim2: parent 2.162,50 != sum(children) 936,00 (2 children)</t>
+          <t>57.02 trim3: parent 1.540,50 != sum(children) 1.028,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62179,12 +62179,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20.04 total_2024: parent 135,00 != sum(children) 99,00 (2 children)</t>
+          <t>20.04 trim4: parent 14,00 != sum(children) 11,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62209,12 +62209,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20.04 trim4: parent 14,00 != sum(children) 11,00 (2 children)</t>
+          <t>20.04 trim2: parent 49,00 != sum(children) 39,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62239,12 +62239,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20.04 trim3: parent 24,00 != sum(children) 16,00 (2 children)</t>
+          <t>20.04 trim1: parent 48,00 != sum(children) 33,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62269,12 +62269,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20.04 trim1: parent 48,00 != sum(children) 33,00 (2 children)</t>
+          <t>20.04 total_2024: parent 135,00 != sum(children) 99,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62299,12 +62299,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20.04 trim2: parent 49,00 != sum(children) 39,00 (2 children)</t>
+          <t>20.04 trim3: parent 24,00 != sum(children) 16,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62359,12 +62359,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>67.02 total_2024: parent 22.404,85 != sum(children) 149,05 (1 children)</t>
+          <t>67.02 trim1: parent 7.985,50 != sum(children) 74,50 (1 children)</t>
         </is>
       </c>
     </row>
@@ -62389,12 +62389,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>67.02 trim1: parent 7.985,50 != sum(children) 74,50 (1 children)</t>
+          <t>67.02 total_2024: parent 22.404,85 != sum(children) 149,05 (1 children)</t>
         </is>
       </c>
     </row>
@@ -62504,12 +62504,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>68.02 total_2024: parent 36.786,00 != sum(children) 138,00 (1 children)</t>
+          <t>68.02 trim1: parent 11.285,20 != sum(children) 30,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -62534,12 +62534,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>68.02 trim1: parent 11.285,20 != sum(children) 30,00 (1 children)</t>
+          <t>68.02 total_2024: parent 36.786,00 != sum(children) 138,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -62589,12 +62589,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 1.825,00 != sum(children) 1.785,00 (8 children)</t>
+          <t>20.01 trim4: parent 102,35 != sum(children) 92,35 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62619,12 +62619,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 102,35 != sum(children) 92,35 (8 children)</t>
+          <t>20.01 trim2: parent 485,30 != sum(children) 475,30 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62649,12 +62649,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 108,05 != sum(children) 98,05 (8 children)</t>
+          <t>20.01 trim1: parent 1.129,30 != sum(children) 1.119,30 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62679,12 +62679,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 1.129,30 != sum(children) 1.119,30 (8 children)</t>
+          <t>20.01 total_2024: parent 1.825,00 != sum(children) 1.785,00 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62709,12 +62709,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>20.01 trim2: parent 485,30 != sum(children) 475,30 (8 children)</t>
+          <t>20.01 trim3: parent 108,05 != sum(children) 98,05 (8 children)</t>
         </is>
       </c>
     </row>
@@ -62739,12 +62739,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>71.01 total_2024: parent 138,00 != sum(children) 50,70 (3 children)</t>
+          <t>71.01 trim2: parent 108,00 != sum(children) 18,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62769,12 +62769,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>71.01 trim2: parent 108,00 != sum(children) 18,00 (3 children)</t>
+          <t>71.01 total_2024: parent 138,00 != sum(children) 50,70 (3 children)</t>
         </is>
       </c>
     </row>
@@ -62829,12 +62829,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 485.803,89 != sum(children) 135.037,13 (2 children)</t>
+          <t>70.02 trim4: parent 143.895,26 != sum(children) 31.123,08 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62859,12 +62859,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.02 trim4: parent 143.895,26 != sum(children) 31.123,08 (2 children)</t>
+          <t>70.02 est2027: parent 82.240,00 != sum(children) 68.500,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62889,12 +62889,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.02 trim3: parent 164.605,24 != sum(children) 29.587,56 (2 children)</t>
+          <t>70.02 trim2: parent 77.154,34 != sum(children) 24.605,44 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62919,12 +62919,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>70.02 est2026: parent 417.259,65 != sum(children) 289.551,61 (2 children)</t>
+          <t>70.02 trim1: parent 100.149,05 != sum(children) 49.721,05 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62949,12 +62949,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>70.02 est2024: parent 537.737,77 != sum(children) 197.921,55 (2 children)</t>
+          <t>70.02 est2026: parent 417.259,65 != sum(children) 289.551,61 (2 children)</t>
         </is>
       </c>
     </row>
@@ -62979,12 +62979,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.02 trim1: parent 100.149,05 != sum(children) 49.721,05 (2 children)</t>
+          <t>70.02 total_2024: parent 485.803,89 != sum(children) 135.037,13 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63009,12 +63009,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>70.02 trim2: parent 77.154,34 != sum(children) 24.605,44 (2 children)</t>
+          <t>70.02 trim3: parent 164.605,24 != sum(children) 29.587,56 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63039,12 +63039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.02 est2027: parent 82.240,00 != sum(children) 68.500,00 (2 children)</t>
+          <t>70.02 est2024: parent 537.737,77 != sum(children) 197.921,55 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63094,12 +63094,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 14.731,99 != sum(children) 4.975,60 (7 children)</t>
+          <t>20.01 trim4: parent 259,60 != sum(children) 559,60 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63124,12 +63124,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 259,60 != sum(children) 559,60 (7 children)</t>
+          <t>20.01 trim2: parent 2.965,00 != sum(children) 1.765,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63154,12 +63154,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 7.190,99 != sum(children) 1.180,00 (7 children)</t>
+          <t>20.01 trim1: parent 4.316,40 != sum(children) 1.471,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63184,12 +63184,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 4.316,40 != sum(children) 1.471,00 (7 children)</t>
+          <t>20.01 total_2024: parent 14.731,99 != sum(children) 4.975,60 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63214,12 +63214,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>20.01 trim2: parent 2.965,00 != sum(children) 1.765,00 (7 children)</t>
+          <t>20.01 trim3: parent 7.190,99 != sum(children) 1.180,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -63244,12 +63244,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>58 total_2024: parent 21.548,02 != sum(children) 2.521,00 (2 children)</t>
+          <t>58 trim4: parent 2.951,01 != sum(children) 10,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63274,12 +63274,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>58 trim4: parent 2.951,01 != sum(children) 10,00 (2 children)</t>
+          <t>58 trim2: parent 7.326,20 != sum(children) 220,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63304,12 +63304,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>58 trim3: parent 3.246,81 != sum(children) 2.220,00 (2 children)</t>
+          <t>58 trim1: parent 8.024,00 != sum(children) 71,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63334,12 +63334,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>58 trim1: parent 8.024,00 != sum(children) 71,00 (2 children)</t>
+          <t>58 total_2024: parent 21.548,02 != sum(children) 2.521,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63364,12 +63364,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>58 trim2: parent 7.326,20 != sum(children) 220,00 (2 children)</t>
+          <t>58 trim3: parent 3.246,81 != sum(children) 2.220,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -63564,12 +63564,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 2.325,30 != sum(children) 2.209,80 (9 children)</t>
+          <t>20.01 trim4: parent -385,20 != sum(children) -391,70 (9 children)</t>
         </is>
       </c>
     </row>
@@ -63594,12 +63594,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent -385,20 != sum(children) -391,70 (9 children)</t>
+          <t>20.01 trim2: parent 415,90 != sum(children) 345,90 (9 children)</t>
         </is>
       </c>
     </row>
@@ -63624,12 +63624,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 892,10 != sum(children) 883,10 (9 children)</t>
+          <t>20.01 trim1: parent 1.402,50 != sum(children) 1.372,50 (9 children)</t>
         </is>
       </c>
     </row>
@@ -63654,12 +63654,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 1.402,50 != sum(children) 1.372,50 (9 children)</t>
+          <t>20.01 total_2024: parent 2.325,30 != sum(children) 2.209,80 (9 children)</t>
         </is>
       </c>
     </row>
@@ -63684,12 +63684,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>20.01 trim2: parent 415,90 != sum(children) 345,90 (9 children)</t>
+          <t>20.01 trim3: parent 892,10 != sum(children) 883,10 (9 children)</t>
         </is>
       </c>
     </row>
@@ -64204,7 +64204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -64230,7 +64230,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -64330,27 +64330,27 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Pagini asteptate</t>
+          <t>Linii anexe separate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Pagini selectate</t>
+          <t>Celule numerice anexe separate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Pagini procesate</t>
+          <t>Pagini asteptate</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -64360,115 +64360,111 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDF complet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
+          <t>Pagini procesate</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1140</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>% curat</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>95.2</v>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>127</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>% curat</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Informatii</t>
+          <t>Erori</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Schema publicare</t>
+          <t>Avertismente</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Bundle conversie</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>63f61051ea58044276e1b967</t>
-        </is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 sursa</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>8c47ce1b2d434eecce862fc295fcd30b18ea2dd79e48bf9de1e48779eace62ed</t>
-        </is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Format sursa</t>
+          <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>0e06b5f986513a368be7d754</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 PDF sursa</t>
+          <t>SHA-256 sursa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -64480,10 +64476,34 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Format sursa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8c47ce1b2d434eecce862fc295fcd30b18ea2dd79e48bf9de1e48779eace62ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>local, pag. 1-42, 1226 linii</t>
         </is>
